--- a/public/templates/activity-import-template.xlsx
+++ b/public/templates/activity-import-template.xlsx
@@ -569,7 +569,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>עירוני</t>
+          <t>פסג"ה חולון</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -2584,7 +2584,7 @@
       <formula1>=רשימות!$A$2:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="מקור" error="בחרו מקור מהרשימה." type="list">
-      <formula1>=רשימות!$B$2:$B$6</formula1>
+      <formula1>=רשימות!$B$2:$B$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2597,7 +2597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>משרד החינוך</t>
+          <t>פסג"ה חולון</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ארצי</t>
+          <t>משרד החינוך</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>ארצי</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
           <t>עולמי</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>כללי</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2857,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>אחד מתוך: עירוני / בית ספרי / משרד החינוך / ארצי / עולמי. ריק = עירוני.</t>
+          <t>אחד מתוך: עירוני / בית ספרי / פסג"ה חולון / משרד החינוך / ארצי / עולמי / כללי. ריק = עירוני.</t>
         </is>
       </c>
     </row>

--- a/public/templates/activity-import-template.xlsx
+++ b/public/templates/activity-import-template.xlsx
@@ -2580,7 +2580,7 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="עיקרון" error="בחרו עיקרון מהרשימה." type="list">
+    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="עיקרון" prompt="בחרו מהרשימה. לכמה עקרונות: הקלידו את השמות מופרדים בנקודה-פסיק (;)" type="list">
       <formula1>=רשימות!$A$2:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="מקור" error="בחרו מקור מהרשימה." type="list">
@@ -2756,7 +2756,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>5. פעילות שמתאימה לכמה עקרונות: שורה נפרדת לכל עיקרון, או לציין עיקרון אחד ולשייך את השאר בזמן הטעינה במערכת.</t>
+          <t>5. פעילות שמתאימה לכמה עקרונות: כותבים בתא 'עיקרון' את כל השמות מופרדים בנקודה-פסיק, למשל: הטמעת AI כתשתית; גיוון במרחבי ובסביבות הלמידה. (הרשימה הנפתחת היא עזר לבחירה, אפשר גם להקליד.) גם שורה נפרדת לכל עיקרון עם אותו שם פעילות תאוחד לפעילות אחת בטעינה.</t>
         </is>
       </c>
     </row>
@@ -2869,10 +2869,11 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>חובה. אחד מחמשת העקרונות (רשימה נפתחת). פעילות שמתאימה לכמה עקרונות: שורה נפרדת לכל עיקרון, או שיוך ידני בזמן הטעינה.</t>
-        </is>
-      </c>
-    </row>
+          <t>חובה. שם העיקרון מהרשימה הנפתחת. לכמה עקרונות: השמות מופרדים בנקודה-פסיק (;) באותו תא.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
